--- a/mapping/impix/s1/S1_KPI정의서_IMPIX.xlsx
+++ b/mapping/impix/s1/S1_KPI정의서_IMPIX.xlsx
@@ -559,7 +559,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>2026-10-22 14:45</t>
+          <t>2026-10-22 17:46</t>
         </is>
       </c>
     </row>
